--- a/dados/excel/quadro_escolaridade_secretaria.xlsx
+++ b/dados/excel/quadro_escolaridade_secretaria.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Dados" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dados'!$A$1:$G$189</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
@@ -627,7 +627,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>24/09/2026 19:18</t>
+          <t>10/10/2026 14:55</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -958,19 +958,19 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D6" s="9" t="n">
         <v>12</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>1356632.71</v>
+        <v>1388977.05</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>8532.281194968553</v>
+        <v>8627.186645962733</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>5440.15</v>
+        <v>5582.55</v>
       </c>
     </row>
     <row r="7">
@@ -1012,19 +1012,19 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>4381754.72</v>
+        <v>4497633.22</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>18031.91242798354</v>
+        <v>17990.53288</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>20813.73</v>
+        <v>20801.23</v>
       </c>
     </row>
     <row r="9">
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>8</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>417262.39</v>
+        <v>434563.76</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>5215.779875</v>
+        <v>5364.984691358025</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>3021.935</v>
+        <v>3076.3</v>
       </c>
     </row>
     <row r="10">
@@ -1066,19 +1066,19 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="D10" s="9" t="n">
         <v>15</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>1902756.08</v>
+        <v>1937473.15</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>3338.168561403509</v>
+        <v>3346.240328151986</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>3256.295</v>
+        <v>3275.55</v>
       </c>
     </row>
     <row r="11">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>2573</v>
+        <v>2615</v>
       </c>
       <c r="D11" s="12" t="n">
         <v>63</v>
       </c>
       <c r="E11" s="13" t="n">
-        <v>9735248.710000001</v>
+        <v>9932508.73</v>
       </c>
       <c r="F11" s="13" t="n">
-        <v>3783.617842984843</v>
+        <v>3798.282497131931</v>
       </c>
       <c r="G11" s="13" t="n">
-        <v>3805.36</v>
+        <v>3823.27</v>
       </c>
     </row>
     <row r="12">
@@ -1120,19 +1120,19 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>6297</v>
+        <v>6391</v>
       </c>
       <c r="D12" s="9" t="n">
         <v>171</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>28840696.02</v>
+        <v>29400828.29</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>4580.069242496427</v>
+        <v>4600.348660616492</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>4079.1</v>
+        <v>4087</v>
       </c>
     </row>
     <row r="13">
@@ -1147,16 +1147,16 @@
         </is>
       </c>
       <c r="C13" s="12" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D13" s="12" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="13" t="n">
-        <v>389229.55</v>
+        <v>396512.23</v>
       </c>
       <c r="F13" s="13" t="n">
-        <v>3089.123412698413</v>
+        <v>3097.751796875</v>
       </c>
       <c r="G13" s="13" t="n">
         <v>3249.32</v>
@@ -1174,19 +1174,19 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>917</v>
+        <v>933</v>
       </c>
       <c r="D14" s="9" t="n">
         <v>20</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>6757702.98</v>
+        <v>6895644.49</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>7369.359847328244</v>
+        <v>7390.830107181137</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>6764.55</v>
+        <v>6822.16</v>
       </c>
     </row>
     <row r="15">
@@ -1201,19 +1201,19 @@
         </is>
       </c>
       <c r="C15" s="12" t="n">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>17</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>6226381.17</v>
+        <v>6356688.23</v>
       </c>
       <c r="F15" s="13" t="n">
-        <v>10308.57809602649</v>
+        <v>10336.07842276423</v>
       </c>
       <c r="G15" s="13" t="n">
-        <v>8689.290000000001</v>
+        <v>8758.280000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1228,16 +1228,16 @@
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>586298.29</v>
+        <v>592435.74</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2916.906915422886</v>
+        <v>2918.402660098522</v>
       </c>
       <c r="G16" s="10" t="n">
         <v>2805.14</v>
@@ -1282,19 +1282,19 @@
         </is>
       </c>
       <c r="C18" s="9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>130468.31</v>
+        <v>135449.24</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>3727.666</v>
+        <v>3660.79027027027</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>4259.78</v>
+        <v>4217.44</v>
       </c>
     </row>
     <row r="19">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C19" s="12" t="n">
-        <v>3000</v>
+        <v>3065</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E19" s="13" t="n">
-        <v>13169234.51</v>
+        <v>13501601.37</v>
       </c>
       <c r="F19" s="13" t="n">
-        <v>4389.744836666667</v>
+        <v>4405.090169657422</v>
       </c>
       <c r="G19" s="13" t="n">
-        <v>3937.24</v>
+        <v>3952.79</v>
       </c>
     </row>
     <row r="20">
@@ -1336,19 +1336,19 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>1381096.46</v>
+        <v>1410137.45</v>
       </c>
       <c r="F20" s="10" t="n">
-        <v>3327.943277108433</v>
+        <v>3310.181807511737</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>2820.14</v>
+        <v>2806.71</v>
       </c>
     </row>
     <row r="21">
@@ -1363,19 +1363,19 @@
         </is>
       </c>
       <c r="C21" s="12" t="n">
-        <v>12481</v>
+        <v>12703</v>
       </c>
       <c r="D21" s="12" t="n">
         <v>312</v>
       </c>
       <c r="E21" s="13" t="n">
-        <v>95027401.70999999</v>
+        <v>97164055.56999999</v>
       </c>
       <c r="F21" s="13" t="n">
-        <v>7613.76505969073</v>
+        <v>7648.906208769581</v>
       </c>
       <c r="G21" s="13" t="n">
-        <v>6872.11</v>
+        <v>6890.35</v>
       </c>
     </row>
     <row r="22">
@@ -1390,19 +1390,19 @@
         </is>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2447</v>
+        <v>2479</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>45</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>22927538</v>
+        <v>23358337.32</v>
       </c>
       <c r="F22" s="10" t="n">
-        <v>9369.651818553331</v>
+        <v>9422.483791851553</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>8403.01</v>
+        <v>8429.059999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1417,19 +1417,19 @@
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D23" s="12" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>890774.7</v>
+        <v>931864.3</v>
       </c>
       <c r="F23" s="13" t="n">
-        <v>10008.70449438202</v>
+        <v>10020.04623655914</v>
       </c>
       <c r="G23" s="13" t="n">
-        <v>8701.83</v>
+        <v>9122.120000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1444,19 +1444,19 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>675653.42</v>
+        <v>690037.75</v>
       </c>
       <c r="F24" s="10" t="n">
-        <v>9936.079705882354</v>
+        <v>10000.54710144928</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>9344.575000000001</v>
+        <v>9815.209999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1471,19 +1471,19 @@
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="E25" s="13" t="n">
-        <v>540074.84</v>
+        <v>546142.88</v>
       </c>
       <c r="F25" s="13" t="n">
-        <v>4091.47606060606</v>
+        <v>4106.337443609023</v>
       </c>
       <c r="G25" s="13" t="n">
-        <v>4054.545</v>
+        <v>4054.55</v>
       </c>
     </row>
     <row r="26">
@@ -1498,19 +1498,19 @@
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>720852.11</v>
+        <v>725711.76</v>
       </c>
       <c r="F26" s="10" t="n">
-        <v>3774.094816753927</v>
+        <v>3779.74875</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>3658.25</v>
+        <v>3659.785</v>
       </c>
     </row>
     <row r="27">
@@ -1525,19 +1525,19 @@
         </is>
       </c>
       <c r="C27" s="12" t="n">
-        <v>4366</v>
+        <v>4437</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E27" s="13" t="n">
-        <v>12829903.06</v>
+        <v>13132512.67</v>
       </c>
       <c r="F27" s="13" t="n">
-        <v>2938.594379294549</v>
+        <v>2959.772970475547</v>
       </c>
       <c r="G27" s="13" t="n">
-        <v>3308.75</v>
+        <v>3308.76</v>
       </c>
     </row>
     <row r="28">
@@ -1552,19 +1552,19 @@
         </is>
       </c>
       <c r="C28" s="9" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>7</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>1213680.33</v>
+        <v>1250578.48</v>
       </c>
       <c r="F28" s="10" t="n">
-        <v>3298.044375</v>
+        <v>3352.757319034853</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>3551.44</v>
+        <v>3555.98</v>
       </c>
     </row>
     <row r="29">
@@ -1579,16 +1579,16 @@
         </is>
       </c>
       <c r="C29" s="12" t="n">
-        <v>93596</v>
+        <v>95107</v>
       </c>
       <c r="D29" s="12" t="n">
-        <v>2600</v>
+        <v>2646</v>
       </c>
       <c r="E29" s="13" t="n">
-        <v>307611087.26</v>
+        <v>314328147.23</v>
       </c>
       <c r="F29" s="13" t="n">
-        <v>3286.583692251806</v>
+        <v>3304.994871355421</v>
       </c>
       <c r="G29" s="13" t="n">
         <v>3491.88</v>
@@ -1606,16 +1606,16 @@
         </is>
       </c>
       <c r="C30" s="9" t="n">
-        <v>43728</v>
+        <v>44351</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>3319</v>
+        <v>3354</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>66841498.04</v>
+        <v>68226307.28</v>
       </c>
       <c r="F30" s="10" t="n">
-        <v>1528.574324002927</v>
+        <v>1538.326244729544</v>
       </c>
       <c r="G30" s="10" t="n">
         <v>1084.8</v>
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="C31" s="12" t="n">
-        <v>236688</v>
+        <v>241746</v>
       </c>
       <c r="D31" s="12" t="n">
-        <v>9415</v>
+        <v>9674</v>
       </c>
       <c r="E31" s="13" t="n">
-        <v>1168086738.96</v>
+        <v>1199168060.45</v>
       </c>
       <c r="F31" s="13" t="n">
-        <v>4935.13291320219</v>
+        <v>4960.446338098665</v>
       </c>
       <c r="G31" s="13" t="n">
-        <v>3725.57</v>
+        <v>3740.08</v>
       </c>
     </row>
     <row r="32">
@@ -1660,19 +1660,19 @@
         </is>
       </c>
       <c r="C32" s="9" t="n">
-        <v>105198</v>
+        <v>106719</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2223</v>
+        <v>2227</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>1045666624.01</v>
+        <v>1067266000.32</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>9939.985779292381</v>
+        <v>10000.71215359964</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>9901.74</v>
+        <v>9952.43</v>
       </c>
     </row>
     <row r="33">
@@ -1687,19 +1687,19 @@
         </is>
       </c>
       <c r="C33" s="12" t="n">
-        <v>4627</v>
+        <v>4693</v>
       </c>
       <c r="D33" s="12" t="n">
         <v>81</v>
       </c>
       <c r="E33" s="13" t="n">
-        <v>64035443.64</v>
+        <v>65364324.47</v>
       </c>
       <c r="F33" s="13" t="n">
-        <v>13839.51667170953</v>
+        <v>13928.04697847859</v>
       </c>
       <c r="G33" s="13" t="n">
-        <v>12604.68</v>
+        <v>12673.9</v>
       </c>
     </row>
     <row r="34">
@@ -1714,19 +1714,19 @@
         </is>
       </c>
       <c r="C34" s="9" t="n">
-        <v>824</v>
+        <v>834</v>
       </c>
       <c r="D34" s="9" t="n">
         <v>15</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>11013881.69</v>
+        <v>11208469.75</v>
       </c>
       <c r="F34" s="10" t="n">
-        <v>13366.36127427184</v>
+        <v>13439.41217026379</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>12545.4</v>
+        <v>12708.85</v>
       </c>
     </row>
     <row r="35">
@@ -1741,19 +1741,19 @@
         </is>
       </c>
       <c r="C35" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D35" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E35" s="13" t="n">
-        <v>217750.87</v>
+        <v>221554.51</v>
       </c>
       <c r="F35" s="13" t="n">
-        <v>2865.143026315789</v>
+        <v>2877.331298701299</v>
       </c>
       <c r="G35" s="13" t="n">
-        <v>3379.035</v>
+        <v>3419.61</v>
       </c>
     </row>
     <row r="36">
@@ -1795,19 +1795,19 @@
         </is>
       </c>
       <c r="C37" s="12" t="n">
-        <v>2372</v>
+        <v>2411</v>
       </c>
       <c r="D37" s="12" t="n">
         <v>81</v>
       </c>
       <c r="E37" s="13" t="n">
-        <v>8741281.92</v>
+        <v>9019422.92</v>
       </c>
       <c r="F37" s="13" t="n">
-        <v>3685.194738617201</v>
+        <v>3740.9468768146</v>
       </c>
       <c r="G37" s="13" t="n">
-        <v>3462.33</v>
+        <v>3498.04</v>
       </c>
     </row>
     <row r="38">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="C38" s="9" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D38" s="9" t="n">
         <v>36</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>1059808.77</v>
+        <v>1078149.38</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>2365.644575892857</v>
+        <v>2390.575121951219</v>
       </c>
       <c r="G38" s="10" t="n">
         <v>1084.8</v>
@@ -1849,19 +1849,19 @@
         </is>
       </c>
       <c r="C39" s="12" t="n">
-        <v>8690</v>
+        <v>8806</v>
       </c>
       <c r="D39" s="12" t="n">
         <v>165</v>
       </c>
       <c r="E39" s="13" t="n">
-        <v>82335772.31999999</v>
+        <v>84114751.91</v>
       </c>
       <c r="F39" s="13" t="n">
-        <v>9474.772418872266</v>
+        <v>9551.981820349762</v>
       </c>
       <c r="G39" s="13" t="n">
-        <v>7695.49</v>
+        <v>7757.870000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1876,19 +1876,19 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>1191</v>
+        <v>1211</v>
       </c>
       <c r="D40" s="9" t="n">
         <v>22</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>17041424.84</v>
+        <v>17419561.76</v>
       </c>
       <c r="F40" s="10" t="n">
-        <v>14308.50112510495</v>
+        <v>14384.44406275805</v>
       </c>
       <c r="G40" s="10" t="n">
-        <v>14301.28</v>
+        <v>14394.66</v>
       </c>
     </row>
     <row r="41">
@@ -1903,19 +1903,19 @@
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D41" s="12" t="n">
         <v>17</v>
       </c>
       <c r="E41" s="13" t="n">
-        <v>1518971.68</v>
+        <v>1555708.12</v>
       </c>
       <c r="F41" s="13" t="n">
-        <v>3894.799179487179</v>
+        <v>3899.017844611529</v>
       </c>
       <c r="G41" s="13" t="n">
-        <v>3778.455</v>
+        <v>3788.73</v>
       </c>
     </row>
     <row r="42">
@@ -1957,19 +1957,19 @@
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>1665</v>
+        <v>1696</v>
       </c>
       <c r="D43" s="12" t="n">
         <v>51</v>
       </c>
       <c r="E43" s="13" t="n">
-        <v>15650029.27</v>
+        <v>16012949.26</v>
       </c>
       <c r="F43" s="13" t="n">
-        <v>9399.416978978979</v>
+        <v>9441.597441037735</v>
       </c>
       <c r="G43" s="13" t="n">
-        <v>9327.299999999999</v>
+        <v>9372.690000000001</v>
       </c>
     </row>
     <row r="44">
@@ -1984,19 +1984,19 @@
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D44" s="9" t="n">
         <v>4</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>2844707.99</v>
+        <v>2899263.8</v>
       </c>
       <c r="F44" s="10" t="n">
-        <v>12422.30563318777</v>
+        <v>12496.82672413793</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>11598.25</v>
+        <v>11552.465</v>
       </c>
     </row>
     <row r="45">
@@ -2011,16 +2011,16 @@
         </is>
       </c>
       <c r="C45" s="12" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D45" s="12" t="n">
         <v>2</v>
       </c>
       <c r="E45" s="13" t="n">
-        <v>1079384.82</v>
+        <v>1100305.68</v>
       </c>
       <c r="F45" s="13" t="n">
-        <v>14391.7976</v>
+        <v>14477.70631578947</v>
       </c>
       <c r="G45" s="13" t="n">
         <v>17617.8</v>
@@ -2038,19 +2038,19 @@
         </is>
       </c>
       <c r="C46" s="9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D46" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>127604.48</v>
+        <v>144715.81</v>
       </c>
       <c r="F46" s="10" t="n">
-        <v>25520.896</v>
+        <v>24119.30166666667</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>17023.27</v>
+        <v>17067.3</v>
       </c>
     </row>
     <row r="47">
@@ -2061,23 +2061,23 @@
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C47" s="12" t="n">
-        <v>162</v>
+        <v>4</v>
       </c>
       <c r="D47" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E47" s="13" t="n">
-        <v>2321115.56</v>
+        <v>1930.24</v>
       </c>
       <c r="F47" s="13" t="n">
-        <v>14327.87382716049</v>
+        <v>482.56</v>
       </c>
       <c r="G47" s="13" t="n">
-        <v>14728.31</v>
+        <v>482.56</v>
       </c>
     </row>
     <row r="48">
@@ -2088,23 +2088,23 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C48" s="9" t="n">
-        <v>44</v>
+        <v>172</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>520047.23</v>
+        <v>2449464.46</v>
       </c>
       <c r="F48" s="10" t="n">
-        <v>11819.25522727273</v>
+        <v>14241.07244186046</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>12647.535</v>
+        <v>14728.31</v>
       </c>
     </row>
     <row r="49">
@@ -2115,50 +2115,50 @@
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C49" s="12" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" s="13" t="n">
-        <v>646224.5</v>
+        <v>549816.49</v>
       </c>
       <c r="F49" s="13" t="n">
-        <v>35901.36111111111</v>
+        <v>11698.22319148936</v>
       </c>
       <c r="G49" s="13" t="n">
-        <v>37498.235</v>
+        <v>12555.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Secretaria da Saúde</t>
+          <t>Secretaria da Mulher</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C50" s="9" t="n">
-        <v>607</v>
+        <v>18</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>4132265.46</v>
+        <v>646224.5</v>
       </c>
       <c r="F50" s="10" t="n">
-        <v>6807.686095551894</v>
+        <v>35901.36111111111</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>6634.87</v>
+        <v>37498.235</v>
       </c>
     </row>
     <row r="51">
@@ -2169,23 +2169,23 @@
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C51" s="12" t="n">
-        <v>4268</v>
+        <v>612</v>
       </c>
       <c r="D51" s="12" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E51" s="13" t="n">
-        <v>19305635.62</v>
+        <v>4213516.81</v>
       </c>
       <c r="F51" s="13" t="n">
-        <v>4523.344803186505</v>
+        <v>6884.831388888888</v>
       </c>
       <c r="G51" s="13" t="n">
-        <v>4357.405</v>
+        <v>6679.235</v>
       </c>
     </row>
     <row r="52">
@@ -2196,23 +2196,23 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C52" s="9" t="n">
-        <v>458</v>
+        <v>4335</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="E52" s="10" t="n">
-        <v>2350812.6</v>
+        <v>19656874.96</v>
       </c>
       <c r="F52" s="10" t="n">
-        <v>5132.778602620087</v>
+        <v>4534.457891580161</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>4861.24</v>
+        <v>4387.5</v>
       </c>
     </row>
     <row r="53">
@@ -2223,23 +2223,23 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C53" s="12" t="n">
-        <v>71050</v>
+        <v>464</v>
       </c>
       <c r="D53" s="12" t="n">
-        <v>1595</v>
+        <v>9</v>
       </c>
       <c r="E53" s="13" t="n">
-        <v>377825150.82</v>
+        <v>2395651.26</v>
       </c>
       <c r="F53" s="13" t="n">
-        <v>5317.736112878255</v>
+        <v>5163.041508620689</v>
       </c>
       <c r="G53" s="13" t="n">
-        <v>5125.49</v>
+        <v>4869.49</v>
       </c>
     </row>
     <row r="54">
@@ -2250,23 +2250,23 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C54" s="9" t="n">
-        <v>5137</v>
+        <v>72478</v>
       </c>
       <c r="D54" s="9" t="n">
-        <v>256</v>
+        <v>1603</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>20981198.28</v>
+        <v>386713467.71</v>
       </c>
       <c r="F54" s="10" t="n">
-        <v>4084.329040295893</v>
+        <v>5335.597942962002</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>2904.45</v>
+        <v>5147.950000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2277,23 +2277,23 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C55" s="12" t="n">
-        <v>73279</v>
+        <v>5223</v>
       </c>
       <c r="D55" s="12" t="n">
-        <v>1586</v>
+        <v>256</v>
       </c>
       <c r="E55" s="13" t="n">
-        <v>834635562.45</v>
+        <v>21362674.58</v>
       </c>
       <c r="F55" s="13" t="n">
-        <v>11389.83286412205</v>
+        <v>4090.11575339843</v>
       </c>
       <c r="G55" s="13" t="n">
-        <v>9011.110000000001</v>
+        <v>2912.22</v>
       </c>
     </row>
     <row r="56">
@@ -2304,23 +2304,23 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C56" s="9" t="n">
-        <v>23602</v>
+        <v>74514</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>383</v>
+        <v>1591</v>
       </c>
       <c r="E56" s="10" t="n">
-        <v>378533321.98</v>
+        <v>851483182.83</v>
       </c>
       <c r="F56" s="10" t="n">
-        <v>16038.18837301924</v>
+        <v>11427.15708229326</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>13489.46</v>
+        <v>9048.785</v>
       </c>
     </row>
     <row r="57">
@@ -2331,23 +2331,23 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C57" s="12" t="n">
-        <v>2881</v>
+        <v>23950</v>
       </c>
       <c r="D57" s="12" t="n">
-        <v>47</v>
+        <v>383</v>
       </c>
       <c r="E57" s="13" t="n">
-        <v>43861213.08</v>
+        <v>385497544.38</v>
       </c>
       <c r="F57" s="13" t="n">
-        <v>15224.30165914613</v>
+        <v>16095.93087181628</v>
       </c>
       <c r="G57" s="13" t="n">
-        <v>12290.2</v>
+        <v>13543.635</v>
       </c>
     </row>
     <row r="58">
@@ -2358,50 +2358,50 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C58" s="9" t="n">
-        <v>1182</v>
+        <v>2925</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E58" s="10" t="n">
-        <v>20527525.36</v>
+        <v>44848383.42</v>
       </c>
       <c r="F58" s="10" t="n">
-        <v>17366.77272419628</v>
+        <v>15332.78065641026</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>14978.595</v>
+        <v>12328.64</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Administração</t>
+          <t>Secretaria da Saúde</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C59" s="12" t="n">
-        <v>817</v>
+        <v>1199</v>
       </c>
       <c r="D59" s="12" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E59" s="13" t="n">
-        <v>5539826.45</v>
+        <v>20954365.81</v>
       </c>
       <c r="F59" s="13" t="n">
-        <v>6780.693329253366</v>
+        <v>17476.53528773978</v>
       </c>
       <c r="G59" s="13" t="n">
-        <v>6584.21</v>
+        <v>15109.63</v>
       </c>
     </row>
     <row r="60">
@@ -2412,23 +2412,23 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C60" s="9" t="n">
-        <v>612</v>
+        <v>826</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>3014308.94</v>
+        <v>5657343.64</v>
       </c>
       <c r="F60" s="10" t="n">
-        <v>4925.341405228758</v>
+        <v>6849.084309927361</v>
       </c>
       <c r="G60" s="10" t="n">
-        <v>4720.57</v>
+        <v>6609.21</v>
       </c>
     </row>
     <row r="61">
@@ -2439,23 +2439,23 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C61" s="12" t="n">
-        <v>337</v>
+        <v>617</v>
       </c>
       <c r="D61" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E61" s="13" t="n">
-        <v>1781465.92</v>
+        <v>3047653.64</v>
       </c>
       <c r="F61" s="13" t="n">
-        <v>5286.249020771513</v>
+        <v>4939.471053484604</v>
       </c>
       <c r="G61" s="13" t="n">
-        <v>5996.02</v>
+        <v>4723.42</v>
       </c>
     </row>
     <row r="62">
@@ -2466,23 +2466,23 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C62" s="9" t="n">
-        <v>2618</v>
+        <v>339</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="E62" s="10" t="n">
-        <v>11599875.58</v>
+        <v>1798164.55</v>
       </c>
       <c r="F62" s="10" t="n">
-        <v>4430.815729564553</v>
+        <v>5304.320206489676</v>
       </c>
       <c r="G62" s="10" t="n">
-        <v>4021.065</v>
+        <v>6040.3</v>
       </c>
     </row>
     <row r="63">
@@ -2493,23 +2493,23 @@
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C63" s="12" t="n">
-        <v>2316</v>
+        <v>2654</v>
       </c>
       <c r="D63" s="12" t="n">
-        <v>201</v>
+        <v>87</v>
       </c>
       <c r="E63" s="13" t="n">
-        <v>3514449.65</v>
+        <v>11809375.95</v>
       </c>
       <c r="F63" s="13" t="n">
-        <v>1517.46530656304</v>
+        <v>4449.651827430293</v>
       </c>
       <c r="G63" s="13" t="n">
-        <v>1084.8</v>
+        <v>4062.6</v>
       </c>
     </row>
     <row r="64">
@@ -2520,23 +2520,23 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C64" s="9" t="n">
-        <v>8379</v>
+        <v>2336</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E64" s="10" t="n">
-        <v>70872683.29000001</v>
+        <v>3556694.67</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>8458.370126506743</v>
+        <v>1522.557649828767</v>
       </c>
       <c r="G64" s="10" t="n">
-        <v>7412.28</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="65">
@@ -2547,50 +2547,50 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C65" s="12" t="n">
-        <v>1148</v>
+        <v>8465</v>
       </c>
       <c r="D65" s="12" t="n">
-        <v>39</v>
+        <v>225</v>
       </c>
       <c r="E65" s="13" t="n">
-        <v>15467325.42</v>
+        <v>71925522.95</v>
       </c>
       <c r="F65" s="13" t="n">
-        <v>13473.2799825784</v>
+        <v>8496.813106910809</v>
       </c>
       <c r="G65" s="13" t="n">
-        <v>10194.63</v>
+        <v>7482.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
+          <t>Secretaria de Administração</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C66" s="9" t="n">
-        <v>143</v>
+        <v>1156</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>737278.72</v>
+        <v>15612281.07</v>
       </c>
       <c r="F66" s="10" t="n">
-        <v>5155.795244755244</v>
+        <v>13505.43345155709</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>4627.19</v>
+        <v>10208.775</v>
       </c>
     </row>
     <row r="67">
@@ -2601,23 +2601,23 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C67" s="12" t="n">
-        <v>1551</v>
+        <v>144</v>
       </c>
       <c r="D67" s="12" t="n">
-        <v>57</v>
+        <v>3</v>
       </c>
       <c r="E67" s="13" t="n">
-        <v>6453600.47</v>
+        <v>745084.79</v>
       </c>
       <c r="F67" s="13" t="n">
-        <v>4160.928736299162</v>
+        <v>5174.199930555556</v>
       </c>
       <c r="G67" s="13" t="n">
-        <v>3688.41</v>
+        <v>4648.53</v>
       </c>
     </row>
     <row r="68">
@@ -2628,23 +2628,23 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C68" s="9" t="n">
-        <v>537</v>
+        <v>1576</v>
       </c>
       <c r="D68" s="9" t="n">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="E68" s="10" t="n">
-        <v>589146.77</v>
+        <v>6582162.46</v>
       </c>
       <c r="F68" s="10" t="n">
-        <v>1097.107579143389</v>
+        <v>4176.49902284264</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>1078.64</v>
+        <v>3720.65</v>
       </c>
     </row>
     <row r="69">
@@ -2655,23 +2655,23 @@
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C69" s="12" t="n">
-        <v>5548</v>
+        <v>556</v>
       </c>
       <c r="D69" s="12" t="n">
-        <v>145</v>
+        <v>74</v>
       </c>
       <c r="E69" s="13" t="n">
-        <v>83765632.54000001</v>
+        <v>608911.65</v>
       </c>
       <c r="F69" s="13" t="n">
-        <v>15098.34760994953</v>
+        <v>1095.164838129497</v>
       </c>
       <c r="G69" s="13" t="n">
-        <v>9811.725</v>
+        <v>1075.56</v>
       </c>
     </row>
     <row r="70">
@@ -2682,23 +2682,23 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C70" s="9" t="n">
-        <v>1086</v>
+        <v>5631</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>32803600.49</v>
+        <v>85556540.36</v>
       </c>
       <c r="F70" s="10" t="n">
-        <v>30205.89363720073</v>
+        <v>15193.84485171373</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>26830.915</v>
+        <v>9891.549999999999</v>
       </c>
     </row>
     <row r="71">
@@ -2709,50 +2709,50 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C71" s="12" t="n">
-        <v>74</v>
+        <v>1103</v>
       </c>
       <c r="D71" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>2628298.71</v>
+        <v>33421832.7</v>
       </c>
       <c r="F71" s="13" t="n">
-        <v>35517.55013513513</v>
+        <v>30300.84560290118</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>37713.88499999999</v>
+        <v>26936.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Comunicação</t>
+          <t>Secretaria de Assuntos Jurídicos e Patrimônio</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C72" s="9" t="n">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>352925.9</v>
+        <v>2684823.31</v>
       </c>
       <c r="F72" s="10" t="n">
-        <v>3878.306593406593</v>
+        <v>35326.6225</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>4002.8</v>
+        <v>37713.88499999999</v>
       </c>
     </row>
     <row r="73">
@@ -2763,23 +2763,23 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C73" s="12" t="n">
-        <v>290</v>
+        <v>94</v>
       </c>
       <c r="D73" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="E73" s="13" t="n">
-        <v>295078</v>
+        <v>369309.54</v>
       </c>
       <c r="F73" s="13" t="n">
-        <v>1017.510344827586</v>
+        <v>3928.824893617021</v>
       </c>
       <c r="G73" s="13" t="n">
-        <v>1084.8</v>
+        <v>4121.65</v>
       </c>
     </row>
     <row r="74">
@@ -2790,23 +2790,23 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C74" s="9" t="n">
-        <v>1552</v>
+        <v>295</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>17007457.06</v>
+        <v>300471.2</v>
       </c>
       <c r="F74" s="10" t="n">
-        <v>10958.41305412371</v>
+        <v>1018.546440677966</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>10632.69</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="75">
@@ -2817,50 +2817,50 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C75" s="12" t="n">
-        <v>153</v>
+        <v>1579</v>
       </c>
       <c r="D75" s="12" t="n">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="E75" s="13" t="n">
-        <v>2108891.85</v>
+        <v>17370659.52</v>
       </c>
       <c r="F75" s="13" t="n">
-        <v>13783.6068627451</v>
+        <v>11001.05099430019</v>
       </c>
       <c r="G75" s="13" t="n">
-        <v>12185.62</v>
+        <v>10647</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Cultura</t>
+          <t>Secretaria de Comunicação</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C76" s="9" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E76" s="10" t="n">
-        <v>467362.96</v>
+        <v>2125250.8</v>
       </c>
       <c r="F76" s="10" t="n">
-        <v>3862.503801652893</v>
+        <v>13800.32987012987</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>3589.57</v>
+        <v>12185.62</v>
       </c>
     </row>
     <row r="77">
@@ -2871,23 +2871,23 @@
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C77" s="12" t="n">
-        <v>184</v>
+        <v>122</v>
       </c>
       <c r="D77" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>502061.11</v>
+        <v>471139.54</v>
       </c>
       <c r="F77" s="13" t="n">
-        <v>2728.592989130434</v>
+        <v>3861.799508196721</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>2397.89</v>
+        <v>3589.57</v>
       </c>
     </row>
     <row r="78">
@@ -2898,23 +2898,23 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C78" s="9" t="n">
-        <v>70</v>
+        <v>186</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>380224.74</v>
+        <v>511438.71</v>
       </c>
       <c r="F78" s="10" t="n">
-        <v>5431.782</v>
+        <v>2749.670483870968</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>5595.095</v>
+        <v>2451.035</v>
       </c>
     </row>
     <row r="79">
@@ -2925,23 +2925,23 @@
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C79" s="12" t="n">
-        <v>1138</v>
+        <v>71</v>
       </c>
       <c r="D79" s="12" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E79" s="13" t="n">
-        <v>4752430.73</v>
+        <v>387834.6</v>
       </c>
       <c r="F79" s="13" t="n">
-        <v>4176.125421792619</v>
+        <v>5462.459154929577</v>
       </c>
       <c r="G79" s="13" t="n">
-        <v>3936.965</v>
+        <v>5633.8</v>
       </c>
     </row>
     <row r="80">
@@ -2952,23 +2952,23 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C80" s="9" t="n">
-        <v>1167</v>
+        <v>1157</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>2608805.96</v>
+        <v>4849137.84</v>
       </c>
       <c r="F80" s="10" t="n">
-        <v>2235.480685518423</v>
+        <v>4191.130371650821</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>1084.8</v>
+        <v>3952.8</v>
       </c>
     </row>
     <row r="81">
@@ -2979,23 +2979,23 @@
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C81" s="12" t="n">
-        <v>1424</v>
+        <v>1188</v>
       </c>
       <c r="D81" s="12" t="n">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="E81" s="13" t="n">
-        <v>13074773.19</v>
+        <v>2655668.21</v>
       </c>
       <c r="F81" s="13" t="n">
-        <v>9181.722745786516</v>
+        <v>2235.410951178451</v>
       </c>
       <c r="G81" s="13" t="n">
-        <v>8017.1</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="82">
@@ -3006,23 +3006,23 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C82" s="9" t="n">
-        <v>410</v>
+        <v>1452</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>4810660.13</v>
+        <v>13397802.76</v>
       </c>
       <c r="F82" s="10" t="n">
-        <v>11733.3173902439</v>
+        <v>9227.136887052342</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>9970.715</v>
+        <v>8045.83</v>
       </c>
     </row>
     <row r="83">
@@ -3033,50 +3033,50 @@
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C83" s="12" t="n">
-        <v>117</v>
+        <v>415</v>
       </c>
       <c r="D83" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E83" s="13" t="n">
-        <v>1263516.16</v>
+        <v>4869159.36</v>
       </c>
       <c r="F83" s="13" t="n">
-        <v>10799.28341880342</v>
+        <v>11732.91412048193</v>
       </c>
       <c r="G83" s="13" t="n">
-        <v>9448.33</v>
+        <v>9935.139999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
+          <t>Secretaria de Cultura</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C84" s="9" t="n">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="D84" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E84" s="10" t="n">
-        <v>48748.72</v>
+        <v>1305895.13</v>
       </c>
       <c r="F84" s="10" t="n">
-        <v>3482.051428571428</v>
+        <v>10882.45941666667</v>
       </c>
       <c r="G84" s="10" t="n">
-        <v>3716.2</v>
+        <v>9580.52</v>
       </c>
     </row>
     <row r="85">
@@ -3087,23 +3087,23 @@
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C85" s="12" t="n">
-        <v>280</v>
+        <v>14</v>
       </c>
       <c r="D85" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="E85" s="13" t="n">
-        <v>972072.78</v>
+        <v>48748.72</v>
       </c>
       <c r="F85" s="13" t="n">
-        <v>3471.6885</v>
+        <v>3482.051428571428</v>
       </c>
       <c r="G85" s="13" t="n">
-        <v>3534.4</v>
+        <v>3716.2</v>
       </c>
     </row>
     <row r="86">
@@ -3114,23 +3114,23 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C86" s="9" t="n">
-        <v>705</v>
+        <v>280</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>3524235.43</v>
+        <v>972072.78</v>
       </c>
       <c r="F86" s="10" t="n">
-        <v>4998.9155035461</v>
+        <v>3471.6885</v>
       </c>
       <c r="G86" s="10" t="n">
-        <v>4169.76</v>
+        <v>3534.4</v>
       </c>
     </row>
     <row r="87">
@@ -3141,23 +3141,23 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C87" s="12" t="n">
-        <v>34</v>
+        <v>705</v>
       </c>
       <c r="D87" s="12" t="n">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="E87" s="13" t="n">
-        <v>59748.07</v>
+        <v>3524235.43</v>
       </c>
       <c r="F87" s="13" t="n">
-        <v>1757.296176470588</v>
+        <v>4998.9155035461</v>
       </c>
       <c r="G87" s="13" t="n">
-        <v>1084.8</v>
+        <v>4169.76</v>
       </c>
     </row>
     <row r="88">
@@ -3168,23 +3168,23 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C88" s="9" t="n">
-        <v>554</v>
+        <v>34</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E88" s="10" t="n">
-        <v>2621613.86</v>
+        <v>59748.07</v>
       </c>
       <c r="F88" s="10" t="n">
-        <v>4732.154981949458</v>
+        <v>1757.296176470588</v>
       </c>
       <c r="G88" s="10" t="n">
-        <v>3252.02</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="89">
@@ -3195,23 +3195,23 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C89" s="12" t="n">
-        <v>352</v>
+        <v>554</v>
       </c>
       <c r="D89" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E89" s="13" t="n">
-        <v>499468.45</v>
+        <v>2621613.86</v>
       </c>
       <c r="F89" s="13" t="n">
-        <v>1418.944460227273</v>
+        <v>4732.154981949458</v>
       </c>
       <c r="G89" s="13" t="n">
-        <v>1084.8</v>
+        <v>3252.02</v>
       </c>
     </row>
     <row r="90">
@@ -3222,23 +3222,23 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C90" s="9" t="n">
-        <v>2004</v>
+        <v>357</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>88</v>
+        <v>37</v>
       </c>
       <c r="E90" s="10" t="n">
-        <v>17446858.17</v>
+        <v>504712.45</v>
       </c>
       <c r="F90" s="10" t="n">
-        <v>8706.017050898205</v>
+        <v>1413.760364145658</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>7780.18</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="91">
@@ -3249,50 +3249,50 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C91" s="12" t="n">
-        <v>304</v>
+        <v>2019</v>
       </c>
       <c r="D91" s="12" t="n">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E91" s="13" t="n">
-        <v>3681024.91</v>
+        <v>17663302.23</v>
       </c>
       <c r="F91" s="13" t="n">
-        <v>12108.63457236842</v>
+        <v>8748.539985141158</v>
       </c>
       <c r="G91" s="13" t="n">
-        <v>12185.62</v>
+        <v>7780.18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
+          <t>Secretaria de Desenvolvimento Econômico, Trabalho e Turismo</t>
         </is>
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C92" s="9" t="n">
-        <v>71</v>
+        <v>304</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>271480.11</v>
+        <v>3681024.91</v>
       </c>
       <c r="F92" s="10" t="n">
-        <v>3823.66352112676</v>
+        <v>12108.63457236842</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>4080.41</v>
+        <v>12185.62</v>
       </c>
     </row>
     <row r="93">
@@ -3303,23 +3303,23 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C93" s="12" t="n">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="D93" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93" s="13" t="n">
-        <v>13379.2</v>
+        <v>297862.62</v>
       </c>
       <c r="F93" s="13" t="n">
-        <v>1029.169230769231</v>
+        <v>3919.245</v>
       </c>
       <c r="G93" s="13" t="n">
-        <v>1084.8</v>
+        <v>4125.190000000001</v>
       </c>
     </row>
     <row r="94">
@@ -3330,23 +3330,23 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C94" s="9" t="n">
-        <v>395</v>
+        <v>16</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E94" s="10" t="n">
-        <v>3893120.4</v>
+        <v>16633.6</v>
       </c>
       <c r="F94" s="10" t="n">
-        <v>9856.001012658227</v>
+        <v>1039.6</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>9919.08</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="95">
@@ -3357,50 +3357,50 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C95" s="12" t="n">
-        <v>38</v>
+        <v>421</v>
       </c>
       <c r="D95" s="12" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="E95" s="13" t="n">
-        <v>700864.0600000001</v>
+        <v>4178474.99</v>
       </c>
       <c r="F95" s="13" t="n">
-        <v>18443.79105263158</v>
+        <v>9925.118741092638</v>
       </c>
       <c r="G95" s="13" t="n">
-        <v>19383.67</v>
+        <v>9945.299999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Esportes e Lazer</t>
+          <t>Secretaria de Empreendedorismo da Micro e Pequena Empresa</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C96" s="9" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>506760.3</v>
+        <v>700864.0600000001</v>
       </c>
       <c r="F96" s="10" t="n">
-        <v>5334.318947368421</v>
+        <v>18443.79105263158</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>5389.06</v>
+        <v>19383.67</v>
       </c>
     </row>
     <row r="97">
@@ -3411,23 +3411,23 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C97" s="12" t="n">
-        <v>381</v>
+        <v>95</v>
       </c>
       <c r="D97" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E97" s="13" t="n">
-        <v>1697825.17</v>
+        <v>506760.3</v>
       </c>
       <c r="F97" s="13" t="n">
-        <v>4456.23404199475</v>
+        <v>5334.318947368421</v>
       </c>
       <c r="G97" s="13" t="n">
-        <v>4257.73</v>
+        <v>5389.06</v>
       </c>
     </row>
     <row r="98">
@@ -3438,23 +3438,23 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C98" s="9" t="n">
-        <v>731</v>
+        <v>390</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>4148801.87</v>
+        <v>1742020.59</v>
       </c>
       <c r="F98" s="10" t="n">
-        <v>5675.515554035568</v>
+        <v>4466.719461538461</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>4593.05</v>
+        <v>4257.73</v>
       </c>
     </row>
     <row r="99">
@@ -3465,23 +3465,23 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C99" s="12" t="n">
-        <v>675</v>
+        <v>750</v>
       </c>
       <c r="D99" s="12" t="n">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E99" s="13" t="n">
-        <v>1019003.62</v>
+        <v>4265590.53</v>
       </c>
       <c r="F99" s="13" t="n">
-        <v>1509.634992592593</v>
+        <v>5687.454040000001</v>
       </c>
       <c r="G99" s="13" t="n">
-        <v>1084.8</v>
+        <v>4600.530000000001</v>
       </c>
     </row>
     <row r="100">
@@ -3492,23 +3492,23 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C100" s="9" t="n">
-        <v>2959</v>
+        <v>685</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="E100" s="10" t="n">
-        <v>30848178.36</v>
+        <v>1029877.38</v>
       </c>
       <c r="F100" s="10" t="n">
-        <v>10425.20390672524</v>
+        <v>1503.470627737226</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>8991.66</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="101">
@@ -3519,23 +3519,23 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C101" s="12" t="n">
-        <v>891</v>
+        <v>3014</v>
       </c>
       <c r="D101" s="12" t="n">
-        <v>16</v>
+        <v>96</v>
       </c>
       <c r="E101" s="13" t="n">
-        <v>10209099.65</v>
+        <v>31516183.24</v>
       </c>
       <c r="F101" s="13" t="n">
-        <v>11458.02429854097</v>
+        <v>10456.59696084937</v>
       </c>
       <c r="G101" s="13" t="n">
-        <v>8741.24</v>
+        <v>8998.799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -3546,50 +3546,50 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C102" s="9" t="n">
-        <v>141</v>
+        <v>902</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>1753144.59</v>
+        <v>10518167.67</v>
       </c>
       <c r="F102" s="10" t="n">
-        <v>12433.64957446809</v>
+        <v>11660.93976718404</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>12052.04</v>
+        <v>8836.34</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Gabinete Central</t>
+          <t>Secretaria de Esportes e Lazer</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C103" s="12" t="n">
-        <v>1</v>
+        <v>142</v>
       </c>
       <c r="D103" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" s="13" t="n">
-        <v>454.86</v>
+        <v>1769882.16</v>
       </c>
       <c r="F103" s="13" t="n">
-        <v>454.86</v>
+        <v>12463.95887323944</v>
       </c>
       <c r="G103" s="13" t="n">
-        <v>454.86</v>
+        <v>12052.04</v>
       </c>
     </row>
     <row r="104">
@@ -3600,23 +3600,23 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C104" s="9" t="n">
-        <v>811</v>
+        <v>1</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>3578159.57</v>
+        <v>454.86</v>
       </c>
       <c r="F104" s="10" t="n">
-        <v>4412.033995067817</v>
+        <v>454.86</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>3985.93</v>
+        <v>454.86</v>
       </c>
     </row>
     <row r="105">
@@ -3627,23 +3627,23 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C105" s="12" t="n">
-        <v>482</v>
+        <v>841</v>
       </c>
       <c r="D105" s="12" t="n">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E105" s="13" t="n">
-        <v>511428.64</v>
+        <v>3725083.76</v>
       </c>
       <c r="F105" s="13" t="n">
-        <v>1061.055269709543</v>
+        <v>4429.350487514863</v>
       </c>
       <c r="G105" s="13" t="n">
-        <v>1084.8</v>
+        <v>4001.57</v>
       </c>
     </row>
     <row r="106">
@@ -3654,23 +3654,23 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C106" s="9" t="n">
-        <v>4383</v>
+        <v>519</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>178</v>
+        <v>77</v>
       </c>
       <c r="E106" s="10" t="n">
-        <v>47037131.5</v>
+        <v>553245.6799999999</v>
       </c>
       <c r="F106" s="10" t="n">
-        <v>10731.7206251426</v>
+        <v>1065.983969171484</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>9972.18</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="107">
@@ -3681,23 +3681,23 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C107" s="12" t="n">
-        <v>961</v>
+        <v>4478</v>
       </c>
       <c r="D107" s="12" t="n">
-        <v>34</v>
+        <v>180</v>
       </c>
       <c r="E107" s="13" t="n">
-        <v>13748196.66</v>
+        <v>48355252.92</v>
       </c>
       <c r="F107" s="13" t="n">
-        <v>14306.13596253902</v>
+        <v>10798.40395712372</v>
       </c>
       <c r="G107" s="13" t="n">
-        <v>11755.2</v>
+        <v>10007.28</v>
       </c>
     </row>
     <row r="108">
@@ -3708,50 +3708,50 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C108" s="9" t="n">
-        <v>74</v>
+        <v>977</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>1397905.78</v>
+        <v>14028592.26</v>
       </c>
       <c r="F108" s="10" t="n">
-        <v>18890.61864864865</v>
+        <v>14358.84571136131</v>
       </c>
       <c r="G108" s="10" t="n">
-        <v>18909.77</v>
+        <v>11794.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Governo</t>
+          <t>Secretaria de Gabinete Central</t>
         </is>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C109" s="12" t="n">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="D109" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E109" s="13" t="n">
-        <v>183474.85</v>
+        <v>1423593.4</v>
       </c>
       <c r="F109" s="13" t="n">
-        <v>7977.167391304348</v>
+        <v>18981.24533333333</v>
       </c>
       <c r="G109" s="13" t="n">
-        <v>7711.7</v>
+        <v>18930.37</v>
       </c>
     </row>
     <row r="110">
@@ -3762,23 +3762,23 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C110" s="9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D110" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>144873.19</v>
+        <v>183474.85</v>
       </c>
       <c r="F110" s="10" t="n">
-        <v>6036.382916666666</v>
+        <v>7977.167391304348</v>
       </c>
       <c r="G110" s="10" t="n">
-        <v>6386.995</v>
+        <v>7711.7</v>
       </c>
     </row>
     <row r="111">
@@ -3789,23 +3789,23 @@
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C111" s="12" t="n">
-        <v>788</v>
+        <v>24</v>
       </c>
       <c r="D111" s="12" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E111" s="13" t="n">
-        <v>5357767.37</v>
+        <v>144873.19</v>
       </c>
       <c r="F111" s="13" t="n">
-        <v>6799.197170050762</v>
+        <v>6036.382916666666</v>
       </c>
       <c r="G111" s="13" t="n">
-        <v>4588.855</v>
+        <v>6386.995</v>
       </c>
     </row>
     <row r="112">
@@ -3816,23 +3816,23 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C112" s="9" t="n">
-        <v>1454</v>
+        <v>816</v>
       </c>
       <c r="D112" s="9" t="n">
-        <v>177</v>
+        <v>42</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>1730399.52</v>
+        <v>5555852.04</v>
       </c>
       <c r="F112" s="10" t="n">
-        <v>1190.095955983494</v>
+        <v>6808.642205882353</v>
       </c>
       <c r="G112" s="10" t="n">
-        <v>1084.8</v>
+        <v>4599.31</v>
       </c>
     </row>
     <row r="113">
@@ -3843,23 +3843,23 @@
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C113" s="12" t="n">
-        <v>4769</v>
+        <v>1474</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>255</v>
+        <v>179</v>
       </c>
       <c r="E113" s="13" t="n">
-        <v>59029246.24</v>
+        <v>1756099.23</v>
       </c>
       <c r="F113" s="13" t="n">
-        <v>12377.69893898092</v>
+        <v>1191.383466757123</v>
       </c>
       <c r="G113" s="13" t="n">
-        <v>12185.62</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="114">
@@ -3870,23 +3870,23 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C114" s="9" t="n">
-        <v>488</v>
+        <v>4846</v>
       </c>
       <c r="D114" s="9" t="n">
-        <v>33</v>
+        <v>261</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>10303677.38</v>
+        <v>60223209.92</v>
       </c>
       <c r="F114" s="10" t="n">
-        <v>21114.09299180328</v>
+        <v>12427.40609162196</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>16100.77</v>
+        <v>12185.62</v>
       </c>
     </row>
     <row r="115">
@@ -3897,50 +3897,50 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C115" s="12" t="n">
-        <v>1</v>
+        <v>498</v>
       </c>
       <c r="D115" s="12" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="E115" s="13" t="n">
-        <v>30501.14</v>
+        <v>10582084.94</v>
       </c>
       <c r="F115" s="13" t="n">
-        <v>30501.14</v>
+        <v>21249.16654618474</v>
       </c>
       <c r="G115" s="13" t="n">
-        <v>30501.14</v>
+        <v>16100.77</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
+          <t>Secretaria de Governo</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C116" s="9" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="D116" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>345445.42</v>
+        <v>30501.14</v>
       </c>
       <c r="F116" s="10" t="n">
-        <v>6168.668214285714</v>
+        <v>30501.14</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>4421.655</v>
+        <v>30501.14</v>
       </c>
     </row>
     <row r="117">
@@ -3951,23 +3951,23 @@
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C117" s="12" t="n">
-        <v>170</v>
+        <v>59</v>
       </c>
       <c r="D117" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E117" s="13" t="n">
-        <v>2502437.87</v>
+        <v>358409.69</v>
       </c>
       <c r="F117" s="13" t="n">
-        <v>14720.22276470588</v>
+        <v>6074.740508474576</v>
       </c>
       <c r="G117" s="13" t="n">
-        <v>14683.61</v>
+        <v>4422.33</v>
       </c>
     </row>
     <row r="118">
@@ -3978,50 +3978,50 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C118" s="9" t="n">
-        <v>24</v>
+        <v>180</v>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E118" s="10" t="n">
-        <v>208782.57</v>
+        <v>2641466.48</v>
       </c>
       <c r="F118" s="10" t="n">
-        <v>8699.27375</v>
+        <v>14674.81377777778</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>10124.655</v>
+        <v>14683.61</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Mobilidade</t>
+          <t>Secretaria de Inclusão e Transtorno do Espectro Autista</t>
         </is>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C119" s="12" t="n">
-        <v>154</v>
+        <v>25</v>
       </c>
       <c r="D119" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E119" s="13" t="n">
-        <v>876680.49</v>
+        <v>222734.58</v>
       </c>
       <c r="F119" s="13" t="n">
-        <v>5692.730454545454</v>
+        <v>8909.3832</v>
       </c>
       <c r="G119" s="13" t="n">
-        <v>5652.775</v>
+        <v>10150.29</v>
       </c>
     </row>
     <row r="120">
@@ -4032,23 +4032,23 @@
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C120" s="9" t="n">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E120" s="10" t="n">
-        <v>22796.4</v>
+        <v>947203.58</v>
       </c>
       <c r="F120" s="10" t="n">
-        <v>991.1478260869565</v>
+        <v>5706.045662650602</v>
       </c>
       <c r="G120" s="10" t="n">
-        <v>1084.8</v>
+        <v>5612.68</v>
       </c>
     </row>
     <row r="121">
@@ -4059,23 +4059,23 @@
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C121" s="12" t="n">
-        <v>497</v>
+        <v>23</v>
       </c>
       <c r="D121" s="12" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E121" s="13" t="n">
-        <v>3871343.83</v>
+        <v>22796.4</v>
       </c>
       <c r="F121" s="13" t="n">
-        <v>7789.424205231388</v>
+        <v>991.1478260869565</v>
       </c>
       <c r="G121" s="13" t="n">
-        <v>4705.03</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="122">
@@ -4086,23 +4086,23 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C122" s="9" t="n">
-        <v>566</v>
+        <v>525</v>
       </c>
       <c r="D122" s="9" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>921193.17</v>
+        <v>4055657.39</v>
       </c>
       <c r="F122" s="10" t="n">
-        <v>1627.549770318021</v>
+        <v>7725.061695238095</v>
       </c>
       <c r="G122" s="10" t="n">
-        <v>1084.8</v>
+        <v>4708.71</v>
       </c>
     </row>
     <row r="123">
@@ -4113,23 +4113,23 @@
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C123" s="12" t="n">
-        <v>1013</v>
+        <v>580</v>
       </c>
       <c r="D123" s="12" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E123" s="13" t="n">
-        <v>12722499.11</v>
+        <v>955186.95</v>
       </c>
       <c r="F123" s="13" t="n">
-        <v>12559.22913129319</v>
+        <v>1646.874051724138</v>
       </c>
       <c r="G123" s="13" t="n">
-        <v>10659.08</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="124">
@@ -4140,23 +4140,23 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C124" s="9" t="n">
-        <v>50</v>
+        <v>1032</v>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>644274.8100000001</v>
+        <v>12992810.12</v>
       </c>
       <c r="F124" s="10" t="n">
-        <v>12885.4962</v>
+        <v>12589.9322868217</v>
       </c>
       <c r="G124" s="10" t="n">
-        <v>12484.66</v>
+        <v>10676.915</v>
       </c>
     </row>
     <row r="125">
@@ -4167,50 +4167,50 @@
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C125" s="12" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="D125" s="12" t="n">
         <v>1</v>
       </c>
       <c r="E125" s="13" t="n">
-        <v>375117.73</v>
+        <v>661014.0600000001</v>
       </c>
       <c r="F125" s="13" t="n">
-        <v>20839.87388888889</v>
+        <v>12961.06</v>
       </c>
       <c r="G125" s="13" t="n">
-        <v>20252.65</v>
+        <v>12484.66</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Parcerias</t>
+          <t>Secretaria de Mobilidade</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C126" s="9" t="n">
-        <v>76</v>
+        <v>19</v>
       </c>
       <c r="D126" s="9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E126" s="10" t="n">
-        <v>602017.92</v>
+        <v>396688.72</v>
       </c>
       <c r="F126" s="10" t="n">
-        <v>7921.288421052632</v>
+        <v>20878.35368421053</v>
       </c>
       <c r="G126" s="10" t="n">
-        <v>8986.629999999999</v>
+        <v>20340.64</v>
       </c>
     </row>
     <row r="127">
@@ -4221,23 +4221,23 @@
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C127" s="12" t="n">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="D127" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E127" s="13" t="n">
-        <v>182211.44</v>
+        <v>636717.91</v>
       </c>
       <c r="F127" s="13" t="n">
-        <v>1035.292272727273</v>
+        <v>7958.973875000001</v>
       </c>
       <c r="G127" s="13" t="n">
-        <v>1084.8</v>
+        <v>8986.629999999999</v>
       </c>
     </row>
     <row r="128">
@@ -4248,23 +4248,23 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C128" s="9" t="n">
-        <v>847</v>
+        <v>187</v>
       </c>
       <c r="D128" s="9" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>9060005.66</v>
+        <v>193326.24</v>
       </c>
       <c r="F128" s="10" t="n">
-        <v>10696.58283353011</v>
+        <v>1033.830160427807</v>
       </c>
       <c r="G128" s="10" t="n">
-        <v>9690.700000000001</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="129">
@@ -4275,50 +4275,50 @@
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C129" s="12" t="n">
-        <v>92</v>
+        <v>890</v>
       </c>
       <c r="D129" s="12" t="n">
-        <v>5</v>
+        <v>51</v>
       </c>
       <c r="E129" s="13" t="n">
-        <v>1233828.79</v>
+        <v>9648845.24</v>
       </c>
       <c r="F129" s="13" t="n">
-        <v>13411.1825</v>
+        <v>10841.39914606742</v>
       </c>
       <c r="G129" s="13" t="n">
-        <v>14384.28</v>
+        <v>9770.02</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
+          <t>Secretaria de Parcerias</t>
         </is>
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C130" s="9" t="n">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="D130" s="9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E130" s="10" t="n">
-        <v>571598.46</v>
+        <v>1299578.85</v>
       </c>
       <c r="F130" s="10" t="n">
-        <v>4465.61296875</v>
+        <v>13537.2796875</v>
       </c>
       <c r="G130" s="10" t="n">
-        <v>4490.535</v>
+        <v>14397.385</v>
       </c>
     </row>
     <row r="131">
@@ -4329,23 +4329,23 @@
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C131" s="12" t="n">
-        <v>2615</v>
+        <v>130</v>
       </c>
       <c r="D131" s="12" t="n">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="E131" s="13" t="n">
-        <v>16498715.47</v>
+        <v>582277.22</v>
       </c>
       <c r="F131" s="13" t="n">
-        <v>6309.260217973231</v>
+        <v>4479.055538461538</v>
       </c>
       <c r="G131" s="13" t="n">
-        <v>5491.16</v>
+        <v>4519.77</v>
       </c>
     </row>
     <row r="132">
@@ -4356,23 +4356,23 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C132" s="9" t="n">
-        <v>1547</v>
+        <v>2680</v>
       </c>
       <c r="D132" s="9" t="n">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="E132" s="10" t="n">
-        <v>2109318.84</v>
+        <v>16983064.34</v>
       </c>
       <c r="F132" s="10" t="n">
-        <v>1363.489877181642</v>
+        <v>6336.964305970149</v>
       </c>
       <c r="G132" s="10" t="n">
-        <v>1084.8</v>
+        <v>5517.98</v>
       </c>
     </row>
     <row r="133">
@@ -4383,23 +4383,23 @@
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C133" s="12" t="n">
-        <v>5442</v>
+        <v>1574</v>
       </c>
       <c r="D133" s="12" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="E133" s="13" t="n">
-        <v>51223729</v>
+        <v>2148545.17</v>
       </c>
       <c r="F133" s="13" t="n">
-        <v>9412.66611539875</v>
+        <v>1365.022344345616</v>
       </c>
       <c r="G133" s="13" t="n">
-        <v>8738.950000000001</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="134">
@@ -4410,23 +4410,23 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C134" s="9" t="n">
-        <v>610</v>
+        <v>5532</v>
       </c>
       <c r="D134" s="9" t="n">
-        <v>16</v>
+        <v>146</v>
       </c>
       <c r="E134" s="10" t="n">
-        <v>8505631.33</v>
+        <v>52358903.15</v>
       </c>
       <c r="F134" s="10" t="n">
-        <v>13943.65791803279</v>
+        <v>9464.733035068692</v>
       </c>
       <c r="G134" s="10" t="n">
-        <v>12436.81</v>
+        <v>8767.834999999999</v>
       </c>
     </row>
     <row r="135">
@@ -4437,50 +4437,50 @@
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C135" s="12" t="n">
-        <v>3</v>
+        <v>621</v>
       </c>
       <c r="D135" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E135" s="13" t="n">
-        <v>39248.41</v>
+        <v>8677634.43</v>
       </c>
       <c r="F135" s="13" t="n">
-        <v>13082.80333333333</v>
+        <v>13973.64642512077</v>
       </c>
       <c r="G135" s="13" t="n">
-        <v>13805.07</v>
+        <v>12441.22</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Recursos Humanos</t>
+          <t>Secretaria de Planejamento e Desenvolvimento Urbano</t>
         </is>
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C136" s="9" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D136" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>6139.44</v>
+        <v>39248.41</v>
       </c>
       <c r="F136" s="10" t="n">
-        <v>1023.24</v>
+        <v>13082.80333333333</v>
       </c>
       <c r="G136" s="10" t="n">
-        <v>1084.8</v>
+        <v>13805.07</v>
       </c>
     </row>
     <row r="137">
@@ -4491,20 +4491,20 @@
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C137" s="12" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D137" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E137" s="13" t="n">
-        <v>30671.76</v>
+        <v>6139.44</v>
       </c>
       <c r="F137" s="13" t="n">
-        <v>929.4472727272727</v>
+        <v>1023.24</v>
       </c>
       <c r="G137" s="13" t="n">
         <v>1084.8</v>
@@ -4518,23 +4518,23 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C138" s="9" t="n">
-        <v>1887</v>
+        <v>33</v>
       </c>
       <c r="D138" s="9" t="n">
-        <v>77</v>
+        <v>4</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>7574832.53</v>
+        <v>30671.76</v>
       </c>
       <c r="F138" s="10" t="n">
-        <v>4014.219676735559</v>
+        <v>929.4472727272727</v>
       </c>
       <c r="G138" s="10" t="n">
-        <v>4135.71</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="139">
@@ -4545,23 +4545,23 @@
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C139" s="12" t="n">
-        <v>755</v>
+        <v>1927</v>
       </c>
       <c r="D139" s="12" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E139" s="13" t="n">
-        <v>2577919.33</v>
+        <v>7796511.31</v>
       </c>
       <c r="F139" s="13" t="n">
-        <v>3414.462688741722</v>
+        <v>4045.93217955371</v>
       </c>
       <c r="G139" s="13" t="n">
-        <v>1084.8</v>
+        <v>4154.63</v>
       </c>
     </row>
     <row r="140">
@@ -4572,23 +4572,23 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C140" s="9" t="n">
-        <v>4352</v>
+        <v>769</v>
       </c>
       <c r="D140" s="9" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="E140" s="10" t="n">
-        <v>35114749.97</v>
+        <v>2614283.34</v>
       </c>
       <c r="F140" s="10" t="n">
-        <v>8068.646592371323</v>
+        <v>3399.588218465539</v>
       </c>
       <c r="G140" s="10" t="n">
-        <v>7435.325</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="141">
@@ -4599,23 +4599,23 @@
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C141" s="12" t="n">
-        <v>1240</v>
+        <v>4420</v>
       </c>
       <c r="D141" s="12" t="n">
-        <v>26</v>
+        <v>115</v>
       </c>
       <c r="E141" s="13" t="n">
-        <v>14316161.42</v>
+        <v>35904316.3</v>
       </c>
       <c r="F141" s="13" t="n">
-        <v>11545.29146774194</v>
+        <v>8123.148484162895</v>
       </c>
       <c r="G141" s="13" t="n">
-        <v>9621.01</v>
+        <v>7496.475</v>
       </c>
     </row>
     <row r="142">
@@ -4626,50 +4626,50 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C142" s="9" t="n">
-        <v>78</v>
+        <v>1256</v>
       </c>
       <c r="D142" s="9" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="E142" s="10" t="n">
-        <v>687948.52</v>
+        <v>14575191.06</v>
       </c>
       <c r="F142" s="10" t="n">
-        <v>8819.85282051282</v>
+        <v>11604.45148089172</v>
       </c>
       <c r="G142" s="10" t="n">
-        <v>7484.65</v>
+        <v>9681.885</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
+          <t>Secretaria de Recursos Humanos</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C143" s="12" t="n">
-        <v>698</v>
+        <v>79</v>
       </c>
       <c r="D143" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="E143" s="13" t="n">
-        <v>8176082.73</v>
+        <v>703389.36</v>
       </c>
       <c r="F143" s="13" t="n">
-        <v>11713.5855730659</v>
+        <v>8903.662784810127</v>
       </c>
       <c r="G143" s="13" t="n">
-        <v>11671.475</v>
+        <v>7526.83</v>
       </c>
     </row>
     <row r="144">
@@ -4680,50 +4680,50 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C144" s="9" t="n">
-        <v>95</v>
+        <v>704</v>
       </c>
       <c r="D144" s="9" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="E144" s="10" t="n">
-        <v>1148771.52</v>
+        <v>8323647.22</v>
       </c>
       <c r="F144" s="10" t="n">
-        <v>12092.33178947368</v>
+        <v>11823.36252840909</v>
       </c>
       <c r="G144" s="10" t="n">
-        <v>12258.38</v>
+        <v>11742.52</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
+          <t>Secretaria de Relações Institucionais e Metropolitanas</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C145" s="12" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D145" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E145" s="13" t="n">
-        <v>116826.88</v>
+        <v>1176023.66</v>
       </c>
       <c r="F145" s="13" t="n">
-        <v>2920.672</v>
+        <v>12123.95525773196</v>
       </c>
       <c r="G145" s="13" t="n">
-        <v>3138.13</v>
+        <v>12258.38</v>
       </c>
     </row>
     <row r="146">
@@ -4734,23 +4734,23 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C146" s="9" t="n">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D146" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E146" s="10" t="n">
-        <v>2518.08</v>
+        <v>120539.78</v>
       </c>
       <c r="F146" s="10" t="n">
-        <v>839.36</v>
+        <v>2939.994634146341</v>
       </c>
       <c r="G146" s="10" t="n">
-        <v>1084.8</v>
+        <v>3138.13</v>
       </c>
     </row>
     <row r="147">
@@ -4761,23 +4761,23 @@
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C147" s="12" t="n">
-        <v>321</v>
+        <v>3</v>
       </c>
       <c r="D147" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E147" s="13" t="n">
-        <v>1112546.77</v>
+        <v>2518.08</v>
       </c>
       <c r="F147" s="13" t="n">
-        <v>3465.877788161994</v>
+        <v>839.36</v>
       </c>
       <c r="G147" s="13" t="n">
-        <v>3787.69</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="148">
@@ -4788,23 +4788,23 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C148" s="9" t="n">
-        <v>472</v>
+        <v>329</v>
       </c>
       <c r="D148" s="9" t="n">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>895801.41</v>
+        <v>1148294.44</v>
       </c>
       <c r="F148" s="10" t="n">
-        <v>1897.884343220339</v>
+        <v>3490.256656534954</v>
       </c>
       <c r="G148" s="10" t="n">
-        <v>1084.8</v>
+        <v>3787.69</v>
       </c>
     </row>
     <row r="149">
@@ -4815,23 +4815,23 @@
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C149" s="12" t="n">
-        <v>881</v>
+        <v>479</v>
       </c>
       <c r="D149" s="12" t="n">
         <v>46</v>
       </c>
       <c r="E149" s="13" t="n">
-        <v>9268886.5</v>
+        <v>927291.9500000001</v>
       </c>
       <c r="F149" s="13" t="n">
-        <v>10520.87003405221</v>
+        <v>1935.89133611691</v>
       </c>
       <c r="G149" s="13" t="n">
-        <v>8575.85</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="150">
@@ -4842,50 +4842,50 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C150" s="9" t="n">
-        <v>53</v>
+        <v>901</v>
       </c>
       <c r="D150" s="9" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="E150" s="10" t="n">
-        <v>446265.55</v>
+        <v>9518079.59</v>
       </c>
       <c r="F150" s="10" t="n">
-        <v>8420.104716981132</v>
+        <v>10563.90631520533</v>
       </c>
       <c r="G150" s="10" t="n">
-        <v>4547.74</v>
+        <v>8610.65</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Segurança Urbana</t>
+          <t>Secretaria de Relações do Trabalho e Qualificação Profissional</t>
         </is>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C151" s="12" t="n">
-        <v>533</v>
+        <v>54</v>
       </c>
       <c r="D151" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E151" s="13" t="n">
-        <v>2741979.81</v>
+        <v>457223.61</v>
       </c>
       <c r="F151" s="13" t="n">
-        <v>5144.427410881801</v>
+        <v>8467.103888888889</v>
       </c>
       <c r="G151" s="13" t="n">
-        <v>5012.15</v>
+        <v>4692.985</v>
       </c>
     </row>
     <row r="152">
@@ -4896,23 +4896,23 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C152" s="9" t="n">
-        <v>757</v>
+        <v>537</v>
       </c>
       <c r="D152" s="9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E152" s="10" t="n">
-        <v>6641436.89</v>
+        <v>2768656.32</v>
       </c>
       <c r="F152" s="10" t="n">
-        <v>8773.364451783355</v>
+        <v>5155.784581005586</v>
       </c>
       <c r="G152" s="10" t="n">
-        <v>8430.559999999999</v>
+        <v>5033.92</v>
       </c>
     </row>
     <row r="153">
@@ -4923,23 +4923,23 @@
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C153" s="12" t="n">
-        <v>462</v>
+        <v>763</v>
       </c>
       <c r="D153" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E153" s="13" t="n">
-        <v>4533182.09</v>
+        <v>6709546.52</v>
       </c>
       <c r="F153" s="13" t="n">
-        <v>9812.082445887445</v>
+        <v>8793.638951507208</v>
       </c>
       <c r="G153" s="13" t="n">
-        <v>8944.154999999999</v>
+        <v>8437.17</v>
       </c>
     </row>
     <row r="154">
@@ -4950,23 +4950,23 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C154" s="9" t="n">
-        <v>15541</v>
+        <v>465</v>
       </c>
       <c r="D154" s="9" t="n">
-        <v>505</v>
+        <v>10</v>
       </c>
       <c r="E154" s="10" t="n">
-        <v>144013266.03</v>
+        <v>4569074.76</v>
       </c>
       <c r="F154" s="10" t="n">
-        <v>9266.666625699761</v>
+        <v>9825.967225806451</v>
       </c>
       <c r="G154" s="10" t="n">
-        <v>8289.530000000001</v>
+        <v>8976.059999999999</v>
       </c>
     </row>
     <row r="155">
@@ -4977,23 +4977,23 @@
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C155" s="12" t="n">
-        <v>1770</v>
+        <v>15978</v>
       </c>
       <c r="D155" s="12" t="n">
-        <v>84</v>
+        <v>505</v>
       </c>
       <c r="E155" s="13" t="n">
-        <v>9383980.459999999</v>
+        <v>147994767.69</v>
       </c>
       <c r="F155" s="13" t="n">
-        <v>5301.683875706214</v>
+        <v>9262.408792714983</v>
       </c>
       <c r="G155" s="13" t="n">
-        <v>2666.155</v>
+        <v>8244.365</v>
       </c>
     </row>
     <row r="156">
@@ -5004,23 +5004,23 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C156" s="9" t="n">
-        <v>8371</v>
+        <v>1806</v>
       </c>
       <c r="D156" s="9" t="n">
-        <v>166</v>
+        <v>84</v>
       </c>
       <c r="E156" s="10" t="n">
-        <v>98382090.40000001</v>
+        <v>9545814.939999999</v>
       </c>
       <c r="F156" s="10" t="n">
-        <v>11752.7285151117</v>
+        <v>5285.611816168327</v>
       </c>
       <c r="G156" s="10" t="n">
-        <v>10480.41</v>
+        <v>2601.195</v>
       </c>
     </row>
     <row r="157">
@@ -5031,23 +5031,23 @@
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C157" s="12" t="n">
-        <v>539</v>
+        <v>8489</v>
       </c>
       <c r="D157" s="12" t="n">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="E157" s="13" t="n">
-        <v>9375295.560000001</v>
+        <v>100192122.66</v>
       </c>
       <c r="F157" s="13" t="n">
-        <v>17393.8693135436</v>
+        <v>11802.58247850159</v>
       </c>
       <c r="G157" s="13" t="n">
-        <v>15644.25</v>
+        <v>10540.46</v>
       </c>
     </row>
     <row r="158">
@@ -5058,50 +5058,50 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C158" s="9" t="n">
-        <v>33</v>
+        <v>546</v>
       </c>
       <c r="D158" s="9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E158" s="10" t="n">
-        <v>459565.73</v>
+        <v>9557278.01</v>
       </c>
       <c r="F158" s="10" t="n">
-        <v>13926.23424242424</v>
+        <v>17504.17217948718</v>
       </c>
       <c r="G158" s="10" t="n">
-        <v>15003.84</v>
+        <v>15912.56</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>Secretaria de Serviços Públicos e Obras</t>
+          <t>Secretaria de Segurança Urbana</t>
         </is>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C159" s="12" t="n">
-        <v>104</v>
+        <v>33</v>
       </c>
       <c r="D159" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E159" s="13" t="n">
-        <v>509725.96</v>
+        <v>459565.73</v>
       </c>
       <c r="F159" s="13" t="n">
-        <v>4901.211153846154</v>
+        <v>13926.23424242424</v>
       </c>
       <c r="G159" s="13" t="n">
-        <v>4924.75</v>
+        <v>15003.84</v>
       </c>
     </row>
     <row r="160">
@@ -5112,23 +5112,23 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C160" s="9" t="n">
-        <v>584</v>
+        <v>105</v>
       </c>
       <c r="D160" s="9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="E160" s="10" t="n">
-        <v>3675419.78</v>
+        <v>516033.54</v>
       </c>
       <c r="F160" s="10" t="n">
-        <v>6293.527020547945</v>
+        <v>4914.605142857143</v>
       </c>
       <c r="G160" s="10" t="n">
-        <v>6419.75</v>
+        <v>4937.94</v>
       </c>
     </row>
     <row r="161">
@@ -5139,23 +5139,23 @@
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C161" s="12" t="n">
-        <v>785</v>
+        <v>591</v>
       </c>
       <c r="D161" s="12" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E161" s="13" t="n">
-        <v>3563494.45</v>
+        <v>3731997.35</v>
       </c>
       <c r="F161" s="13" t="n">
-        <v>4539.483375796179</v>
+        <v>6314.716328257191</v>
       </c>
       <c r="G161" s="13" t="n">
-        <v>4166.84</v>
+        <v>6440.61</v>
       </c>
     </row>
     <row r="162">
@@ -5166,23 +5166,23 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C162" s="9" t="n">
-        <v>79</v>
+        <v>804</v>
       </c>
       <c r="D162" s="9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E162" s="10" t="n">
-        <v>267256.97</v>
+        <v>3657534.78</v>
       </c>
       <c r="F162" s="10" t="n">
-        <v>3382.999620253164</v>
+        <v>4549.172611940298</v>
       </c>
       <c r="G162" s="10" t="n">
-        <v>3611.38</v>
+        <v>4177.86</v>
       </c>
     </row>
     <row r="163">
@@ -5193,23 +5193,23 @@
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C163" s="12" t="n">
-        <v>2698</v>
+        <v>80</v>
       </c>
       <c r="D163" s="12" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="E163" s="13" t="n">
-        <v>11260285.7</v>
+        <v>271481.51</v>
       </c>
       <c r="F163" s="13" t="n">
-        <v>4173.56771682728</v>
+        <v>3393.518875</v>
       </c>
       <c r="G163" s="13" t="n">
-        <v>4056.77</v>
+        <v>3656.19</v>
       </c>
     </row>
     <row r="164">
@@ -5220,23 +5220,23 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C164" s="9" t="n">
-        <v>511</v>
+        <v>2744</v>
       </c>
       <c r="D164" s="9" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="E164" s="10" t="n">
-        <v>2661910.75</v>
+        <v>11532578.8</v>
       </c>
       <c r="F164" s="10" t="n">
-        <v>5209.218688845401</v>
+        <v>4202.834839650146</v>
       </c>
       <c r="G164" s="10" t="n">
-        <v>3963.96</v>
+        <v>4077.07</v>
       </c>
     </row>
     <row r="165">
@@ -5247,23 +5247,23 @@
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C165" s="12" t="n">
-        <v>4613</v>
+        <v>516</v>
       </c>
       <c r="D165" s="12" t="n">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c r="E165" s="13" t="n">
-        <v>47730572.96</v>
+        <v>2702466.34</v>
       </c>
       <c r="F165" s="13" t="n">
-        <v>10346.97007587253</v>
+        <v>5237.337868217054</v>
       </c>
       <c r="G165" s="13" t="n">
-        <v>9417.85</v>
+        <v>4009.28</v>
       </c>
     </row>
     <row r="166">
@@ -5274,23 +5274,23 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C166" s="9" t="n">
-        <v>457</v>
+        <v>4690</v>
       </c>
       <c r="D166" s="9" t="n">
-        <v>10</v>
+        <v>143</v>
       </c>
       <c r="E166" s="10" t="n">
-        <v>5787997.8</v>
+        <v>48689773.89</v>
       </c>
       <c r="F166" s="10" t="n">
-        <v>12665.20306345733</v>
+        <v>10381.61490191898</v>
       </c>
       <c r="G166" s="10" t="n">
-        <v>10699.17</v>
+        <v>9457.52</v>
       </c>
     </row>
     <row r="167">
@@ -5301,50 +5301,50 @@
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C167" s="12" t="n">
-        <v>100</v>
+        <v>464</v>
       </c>
       <c r="D167" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E167" s="13" t="n">
-        <v>1180903.95</v>
+        <v>5950618.01</v>
       </c>
       <c r="F167" s="13" t="n">
-        <v>11809.0395</v>
+        <v>12824.60778017241</v>
       </c>
       <c r="G167" s="13" t="n">
-        <v>11080.645</v>
+        <v>10774.68</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Turismo</t>
+          <t>Secretaria de Serviços Públicos e Obras</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C168" s="9" t="n">
-        <v>33</v>
+        <v>101</v>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>148995.2</v>
+        <v>1198492.99</v>
       </c>
       <c r="F168" s="10" t="n">
-        <v>4515.006060606061</v>
+        <v>11866.26722772277</v>
       </c>
       <c r="G168" s="10" t="n">
-        <v>4725.06</v>
+        <v>11089.49</v>
       </c>
     </row>
     <row r="169">
@@ -5355,23 +5355,23 @@
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C169" s="12" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D169" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E169" s="13" t="n">
-        <v>39391.92</v>
+        <v>158547.56</v>
       </c>
       <c r="F169" s="13" t="n">
-        <v>1010.049230769231</v>
+        <v>4529.930285714286</v>
       </c>
       <c r="G169" s="13" t="n">
-        <v>1084.8</v>
+        <v>4725.06</v>
       </c>
     </row>
     <row r="170">
@@ -5382,23 +5382,23 @@
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C170" s="9" t="n">
-        <v>177</v>
+        <v>43</v>
       </c>
       <c r="D170" s="9" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E170" s="10" t="n">
-        <v>2367904.17</v>
+        <v>44146.32</v>
       </c>
       <c r="F170" s="10" t="n">
-        <v>13377.98966101695</v>
+        <v>1026.658604651163</v>
       </c>
       <c r="G170" s="10" t="n">
-        <v>14384.28</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="171">
@@ -5409,50 +5409,50 @@
       </c>
       <c r="B171" s="11" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C171" s="12" t="n">
-        <v>45</v>
+        <v>185</v>
       </c>
       <c r="D171" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="E171" s="13" t="n">
-        <v>549679</v>
+        <v>2488848.83</v>
       </c>
       <c r="F171" s="13" t="n">
-        <v>12215.08888888889</v>
+        <v>13453.23691891892</v>
       </c>
       <c r="G171" s="13" t="n">
-        <v>12857.83</v>
+        <v>14410.49</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="8" t="inlineStr">
         <is>
-          <t>Secretaria de Urbanismo e Licenciamento</t>
+          <t>Secretaria de Turismo</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C172" s="9" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="D172" s="9" t="n">
         <v>3</v>
       </c>
       <c r="E172" s="10" t="n">
-        <v>110940.25</v>
+        <v>577278.67</v>
       </c>
       <c r="F172" s="10" t="n">
-        <v>3698.008333333333</v>
+        <v>12282.52489361702</v>
       </c>
       <c r="G172" s="10" t="n">
-        <v>3756.91</v>
+        <v>12857.83</v>
       </c>
     </row>
     <row r="173">
@@ -5463,23 +5463,23 @@
       </c>
       <c r="B173" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C173" s="12" t="n">
-        <v>487</v>
+        <v>30</v>
       </c>
       <c r="D173" s="12" t="n">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="E173" s="13" t="n">
-        <v>2465567.23</v>
+        <v>110940.25</v>
       </c>
       <c r="F173" s="13" t="n">
-        <v>5062.766386036961</v>
+        <v>3698.008333333333</v>
       </c>
       <c r="G173" s="13" t="n">
-        <v>4028.56</v>
+        <v>3756.91</v>
       </c>
     </row>
     <row r="174">
@@ -5490,23 +5490,23 @@
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C174" s="9" t="n">
-        <v>370</v>
+        <v>487</v>
       </c>
       <c r="D174" s="9" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>500391.73</v>
+        <v>2465567.23</v>
       </c>
       <c r="F174" s="10" t="n">
-        <v>1352.410081081081</v>
+        <v>5062.766386036961</v>
       </c>
       <c r="G174" s="10" t="n">
-        <v>1084.8</v>
+        <v>4028.56</v>
       </c>
     </row>
     <row r="175">
@@ -5517,23 +5517,23 @@
       </c>
       <c r="B175" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C175" s="12" t="n">
-        <v>1400</v>
+        <v>370</v>
       </c>
       <c r="D175" s="12" t="n">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="E175" s="13" t="n">
-        <v>10372395.47</v>
+        <v>500391.73</v>
       </c>
       <c r="F175" s="13" t="n">
-        <v>7408.853907142858</v>
+        <v>1352.410081081081</v>
       </c>
       <c r="G175" s="13" t="n">
-        <v>6769.805</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="176">
@@ -5544,23 +5544,23 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C176" s="9" t="n">
-        <v>158</v>
+        <v>1400</v>
       </c>
       <c r="D176" s="9" t="n">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>1975733.77</v>
+        <v>10372395.47</v>
       </c>
       <c r="F176" s="10" t="n">
-        <v>12504.64411392405</v>
+        <v>7408.853907142858</v>
       </c>
       <c r="G176" s="10" t="n">
-        <v>10063.1</v>
+        <v>6769.805</v>
       </c>
     </row>
     <row r="177">
@@ -5571,23 +5571,23 @@
       </c>
       <c r="B177" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C177" s="12" t="n">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="D177" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E177" s="13" t="n">
-        <v>145945.63</v>
+        <v>1975733.77</v>
       </c>
       <c r="F177" s="13" t="n">
-        <v>9729.708666666667</v>
+        <v>12504.64411392405</v>
       </c>
       <c r="G177" s="13" t="n">
-        <v>10613.13</v>
+        <v>10063.1</v>
       </c>
     </row>
     <row r="178">
@@ -5598,50 +5598,50 @@
       </c>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>Doutorado</t>
+          <t>Mestrado</t>
         </is>
       </c>
       <c r="C178" s="9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D178" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>49067.89</v>
+        <v>145945.63</v>
       </c>
       <c r="F178" s="10" t="n">
-        <v>16355.96333333333</v>
+        <v>9729.708666666667</v>
       </c>
       <c r="G178" s="10" t="n">
-        <v>16833.55</v>
+        <v>10613.13</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+          <t>Secretaria de Urbanismo e Licenciamento</t>
         </is>
       </c>
       <c r="B179" s="11" t="inlineStr">
         <is>
-          <t>Sem escolaridade formal registrada</t>
+          <t>Doutorado</t>
         </is>
       </c>
       <c r="C179" s="12" t="n">
-        <v>122</v>
+        <v>3</v>
       </c>
       <c r="D179" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E179" s="13" t="n">
-        <v>685031.04</v>
+        <v>49067.89</v>
       </c>
       <c r="F179" s="13" t="n">
-        <v>5615.008524590165</v>
+        <v>16355.96333333333</v>
       </c>
       <c r="G179" s="13" t="n">
-        <v>5241.29</v>
+        <v>16833.55</v>
       </c>
     </row>
     <row r="180">
@@ -5652,23 +5652,23 @@
       </c>
       <c r="B180" s="8" t="inlineStr">
         <is>
-          <t>Fundamental incompleto</t>
+          <t>Sem escolaridade formal registrada</t>
         </is>
       </c>
       <c r="C180" s="9" t="n">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E180" s="10" t="n">
-        <v>763943.79</v>
+        <v>685031.04</v>
       </c>
       <c r="F180" s="10" t="n">
-        <v>5535.824565217392</v>
+        <v>5615.008524590165</v>
       </c>
       <c r="G180" s="10" t="n">
-        <v>5368.025</v>
+        <v>5241.29</v>
       </c>
     </row>
     <row r="181">
@@ -5679,23 +5679,23 @@
       </c>
       <c r="B181" s="11" t="inlineStr">
         <is>
-          <t>Fundamental completo</t>
+          <t>Fundamental incompleto</t>
         </is>
       </c>
       <c r="C181" s="12" t="n">
-        <v>282</v>
+        <v>140</v>
       </c>
       <c r="D181" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E181" s="13" t="n">
-        <v>1424403.14</v>
+        <v>780440.42</v>
       </c>
       <c r="F181" s="13" t="n">
-        <v>5051.074964539007</v>
+        <v>5574.574428571429</v>
       </c>
       <c r="G181" s="13" t="n">
-        <v>5134.155</v>
+        <v>5446.33</v>
       </c>
     </row>
     <row r="182">
@@ -5706,23 +5706,23 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>Medio incompleto</t>
+          <t>Fundamental completo</t>
         </is>
       </c>
       <c r="C182" s="9" t="n">
-        <v>25</v>
+        <v>288</v>
       </c>
       <c r="D182" s="9" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E182" s="10" t="n">
-        <v>188335.02</v>
+        <v>1447220.35</v>
       </c>
       <c r="F182" s="10" t="n">
-        <v>7533.400799999999</v>
+        <v>5025.070659722222</v>
       </c>
       <c r="G182" s="10" t="n">
-        <v>6828.08</v>
+        <v>5120.225</v>
       </c>
     </row>
     <row r="183">
@@ -5733,23 +5733,23 @@
       </c>
       <c r="B183" s="11" t="inlineStr">
         <is>
-          <t>Medio completo</t>
+          <t>Medio incompleto</t>
         </is>
       </c>
       <c r="C183" s="12" t="n">
-        <v>801</v>
+        <v>25</v>
       </c>
       <c r="D183" s="12" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="E183" s="13" t="n">
-        <v>4268176.81</v>
+        <v>188335.02</v>
       </c>
       <c r="F183" s="13" t="n">
-        <v>5328.560312109862</v>
+        <v>7533.400799999999</v>
       </c>
       <c r="G183" s="13" t="n">
-        <v>4562.97</v>
+        <v>6828.08</v>
       </c>
     </row>
     <row r="184">
@@ -5760,23 +5760,23 @@
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>Superior incompleto</t>
+          <t>Medio completo</t>
         </is>
       </c>
       <c r="C184" s="9" t="n">
-        <v>1339</v>
+        <v>825</v>
       </c>
       <c r="D184" s="9" t="n">
-        <v>115</v>
+        <v>37</v>
       </c>
       <c r="E184" s="10" t="n">
-        <v>2384592.84</v>
+        <v>4408345.16</v>
       </c>
       <c r="F184" s="10" t="n">
-        <v>1780.875907393577</v>
+        <v>5343.448678787879</v>
       </c>
       <c r="G184" s="10" t="n">
-        <v>1084.8</v>
+        <v>4596.97</v>
       </c>
     </row>
     <row r="185">
@@ -5787,23 +5787,23 @@
       </c>
       <c r="B185" s="11" t="inlineStr">
         <is>
-          <t>Superior completo</t>
+          <t>Superior incompleto</t>
         </is>
       </c>
       <c r="C185" s="12" t="n">
-        <v>4328</v>
+        <v>1359</v>
       </c>
       <c r="D185" s="12" t="n">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="E185" s="13" t="n">
-        <v>43891101.32</v>
+        <v>2413814.65</v>
       </c>
       <c r="F185" s="13" t="n">
-        <v>10141.19716266174</v>
+        <v>1776.169720382634</v>
       </c>
       <c r="G185" s="13" t="n">
-        <v>9100.5</v>
+        <v>1084.8</v>
       </c>
     </row>
     <row r="186">
@@ -5814,23 +5814,23 @@
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t>Pos-graduacao</t>
+          <t>Superior completo</t>
         </is>
       </c>
       <c r="C186" s="9" t="n">
-        <v>381</v>
+        <v>4427</v>
       </c>
       <c r="D186" s="9" t="n">
-        <v>11</v>
+        <v>158</v>
       </c>
       <c r="E186" s="10" t="n">
-        <v>3306524.24</v>
+        <v>44907831.37</v>
       </c>
       <c r="F186" s="10" t="n">
-        <v>8678.541312335959</v>
+        <v>10144.07756268353</v>
       </c>
       <c r="G186" s="10" t="n">
-        <v>8377.610000000001</v>
+        <v>9126.16</v>
       </c>
     </row>
     <row r="187">
@@ -5841,23 +5841,23 @@
       </c>
       <c r="B187" s="11" t="inlineStr">
         <is>
-          <t>Mestrado</t>
+          <t>Pos-graduacao</t>
         </is>
       </c>
       <c r="C187" s="12" t="n">
-        <v>226</v>
+        <v>389</v>
       </c>
       <c r="D187" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E187" s="13" t="n">
-        <v>1962245.74</v>
+        <v>3373097.17</v>
       </c>
       <c r="F187" s="13" t="n">
-        <v>8682.503274336283</v>
+        <v>8671.200951156812</v>
       </c>
       <c r="G187" s="13" t="n">
-        <v>8508.645</v>
+        <v>8377.610000000001</v>
       </c>
     </row>
     <row r="188">
@@ -5868,27 +5868,54 @@
       </c>
       <c r="B188" s="8" t="inlineStr">
         <is>
+          <t>Mestrado</t>
+        </is>
+      </c>
+      <c r="C188" s="9" t="n">
+        <v>230</v>
+      </c>
+      <c r="D188" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>2007331</v>
+      </c>
+      <c r="F188" s="10" t="n">
+        <v>8727.526086956521</v>
+      </c>
+      <c r="G188" s="10" t="n">
+        <v>8512.700000000001</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="11" t="inlineStr">
+        <is>
+          <t>Secretaria do Meio Ambiente, Parques e Jardins</t>
+        </is>
+      </c>
+      <c r="B189" s="11" t="inlineStr">
+        <is>
           <t>Doutorado</t>
         </is>
       </c>
-      <c r="C188" s="9" t="n">
-        <v>146</v>
-      </c>
-      <c r="D188" s="9" t="n">
+      <c r="C189" s="12" t="n">
+        <v>148</v>
+      </c>
+      <c r="D189" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="E188" s="10" t="n">
-        <v>1904545.53</v>
-      </c>
-      <c r="F188" s="10" t="n">
-        <v>13044.83239726027</v>
-      </c>
-      <c r="G188" s="10" t="n">
-        <v>12052.01</v>
+      <c r="E189" s="13" t="n">
+        <v>1955464.99</v>
+      </c>
+      <c r="F189" s="13" t="n">
+        <v>13212.60128378378</v>
+      </c>
+      <c r="G189" s="13" t="n">
+        <v>12134.11</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G188"/>
+  <autoFilter ref="A1:G189"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>